--- a/backend/result/result_2.xlsx
+++ b/backend/result/result_2.xlsx
@@ -3034,37 +3034,63 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">SELECT 
-  stock_abbr,
-  MIN(report_year) as start_year,
-  MAX(report_year) as end_year,
-  MAX(report_year) - MIN(report_year) as years,
-  FIRST_VALUE(total_operating_revenue) OVER (PARTITION BY stock_abbr ORDER BY report_year) as start_value,
-  LAST_VALUE(total_operating_revenue) OVER (PARTITION BY stock_abbr ORDER BY report_year ROWS BETWEEN UNBOUNDED PRECEDING AND UNBOUNDED FOLLOWING) as end_value,
-  ROUND(
-    (POWER(
-      LAST_VALUE(total_operating_revenue) OVER (PARTITION BY stock_abbr ORDER BY report_year ROWS BETWEEN UNBOUNDED PRECEDING AND UNBOUNDED FOLLOWING) 
-      / NULLIF(FIRST_VALUE(total_operating_revenue) OVER (PARTITION BY stock_abbr ORDER BY report_year), 0),
-      1.0 / NULLIF(MAX(report_year) - MIN(report_year), 0)
-    ) - 1) * 100, 2
-  ) as cagr_rate
-FROM income_sheet
-WHERE 1=1
-  AND report_year BETWEEN 2022 AND 2025
-  AND report_period = 'Q3'
-GROUP BY stock_abbr, report_year, total_operating_revenue
-ORDER BY stock_abbr
-</t>
+          <t>WITH company_list AS (
+  SELECT stock_code, stock_abbr
+  FROM company_basic_info
+  WHERE 1=1
+),
+revenue_data AS (
+  SELECT 
+    i.stock_code,
+    c.stock_abbr,
+    i.report_year,
+    i.total_operating_revenue
+  FROM income_sheet i
+  INNER JOIN company_list c ON i.stock_code = c.stock_code
+  WHERE i.report_period = 'Q3'
+    AND i.report_year IN (2022, 2025)
+),
+start_revenue AS (
+  SELECT stock_code, stock_abbr, total_operating_revenue as start_revenue
+  FROM revenue_data
+  WHERE report_year = 2022
+),
+end_revenue AS (
+  SELECT stock_code, stock_abbr, total_operating_revenue as end_revenue
+  FROM revenue_data
+  WHERE report_year = 2025
+),
+cagr_calc AS (
+  SELECT 
+    e.stock_code,
+    e.stock_abbr,
+    e.end_revenue,
+    s.start_revenue,
+    CASE 
+      WHEN s.start_revenue &gt; 0 THEN (POWER(e.end_revenue / s.start_revenue, 1.0/3) - 1) * 100
+      ELSE NULL 
+    END as cagr
+  FROM end_revenue e
+  INNER JOIN start_revenue s ON e.stock_code = s.stock_code
+)
+SELECT 
+  FLOOR(cagr / 5) * 5 as cagr_bucket,
+  COUNT(*) as company_count,
+  ROUND(COUNT(*) * 100.0 / SUM(COUNT(*)) OVER(), 2) as percentage
+FROM cagr_calc
+WHERE cagr IS NOT NULL
+GROUP BY FLOOR(cagr / 5) * 5
+ORDER BY cagr_bucket</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>图表</t>
+          <t>无</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>[{"A": {"image": ["./result/B1063_1.jpg"], "content": "## 分析结果\n\n### 数据问题说明\n\n当前查询结果**无法计算复合增长率(CAGR)**，原因如下：\n\n1. **years字段全为0**：所有记录的start_year等于end_year，无法计算跨期增长率\n2. **CAGR值全为null**：查询未返回计算结果\n3. **数据单位异常**：部分公司数据存在单位混淆（如千金药业end_value为2718335546.60，明显异常）\n\n### 数据有效性检验\n\n| 异常类型 | 公司示例 | 问题描述 |\n|---------|---------|---------|\n| 单位错误 | 千金药业、康恩贝、达仁堂 | start_value与end_value量级差异过大 |\n| 数据缺失 | 维康药业、莱茵生物 | 数值异常偏离正常范围 |\n| 跨期缺失 | 贵州百灵 | 缺少2024年数据 |\n\n### 正确计算CAGR所需数据格式\n\n```\nCAGR = (End Value / Start Value)^(1/years) - 1\n\n示例（假设有有效数据）：\n- 2022年Q3营业总收入 = 100,000万元\n- 2025年Q3营业总收入 = 150,000万元\n- years = 3\n- CAGR = (150000/100000)^(1/3) - 1 ≈ 14.47%\n```\n\n### 直方图展示\n\n```python\nimport matplotlib.pyplot as plt\nimport numpy as np\n\n# 注：由于原始数据CAGR均为null，此为示意性代码\n# 实际使用时需替换为正确计算的CAGR值\n\n# 示例分布（假设）\ncagr_values = [\n    -15.23, -8.45, -5.67, -2.10, 0.00, 0.00, 1.23, 3.45, 5.67, 8.90,\n    10.12, 12.34, 14.56, 16.78, 18.90, 22.15, 25.67\n]\n\nfig, ax = plt.subplots(figsize=(12, 6))\n\n# 绘制直方图\ncounts, bins, patches = ax.hist(cagr_values, bins=8, edgecolor='black', alpha=0.7)\n\n# 添加均值线\nmean_cagr = np.mean(cagr_values)\nax.axvline(mean_cagr, color='red', linestyle='--', linewidth=2, label=f'均值: {mean_cagr:.2f}%')\n\nax.set_xlabel('复合增长率 (%)', fontsize=12)\nax.set_ylabel('公司数量', fontsize=12)\nax.set_title('2022-2025年Q3中药公司营业总收入CAGR分布', fontsize=14)\nax.legend()\nax.grid(axis='y', alpha=0.3)\n\nplt.tight_layout()\nplt.show()\n```\n\n### 建议\n\n1. **修正查询**：确保获取2022年和2025年Q3的营业总收入数据，years应计算为3\n2. **数据清洗**：统一金额单位（建议全部转换为\"万元\"）\n3. **重新计算**：使用正确格式的数据计算CAGR后，再生成直方图\n\n如需我基于正确数据重新分析，请提供符合以下格式的数据：\n- `stock_abbr`: 公司简称\n- `start_value`: 2022年Q3营业总收入（万元）\n- `end_value`: 2025年Q3营业总收入（万元）\n- `years`: 3"}, "Q": "分析2022-2025年第三季度66家中药公司营业总收入的复合增长率分布，用直方图展示"}]</t>
+          <t>[{"A": {"content": "## 2022-2025年第三季度中药公司营业总收入复合增长率分布分析\n\n### 一、核心发现\n\n| CAGR区间 | 公司数量 | 占比 |\n|---------|---------|------|\n| -100% | 1 | 100.00% |\n\n**分析结论：**\n\n1. **数据高度集中**：在66家中药公司中，仅1家公司（100%）的营业总收入复合增长率为-100%，其余65家公司数据缺失或无法计算。\n\n2. **指标解读**：CAGR为-100%意味着该公司2022年Q3有营业总收入，但至2025年Q3时收入已完全归零。\n\n### 二、计算逻辑说明\n\n$$CAGR = \\left(\\frac{期末值}{期初值}\\right)^{\\frac{1}{n}} - 1$$\n\n- 期初：2022年Q3营业总收入\n- 期末：2025年Q3营业总收入\n- 年数：3年\n\n**-100% CAGR含义**：期末收入/期初收入 = 0，说明公司主营业务已基本停止运营。\n\n### 三、数据说明\n\n当前直方图仅展示1个数据点（-100%区间），无法呈现完整分布。建议：\n\n1. **检查数据完整性**：确认其余65家公司是否缺少期初或期末数据\n2. **扩大区间覆盖**：增加更多CAGR区间以观察分布全貌\n\n如需补充完整分布数据或进一步分析具体公司情况，请提供原始查询数据。"}, "Q": "分析2022-2025年第三季度66家中药公司营业总收入的复合增长率分布，用直方图展示"}]</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3176,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>[{"A": {"content": "抱歉，数据库中没有出口业务相关字段。请尝试其他问题或换一种表述方式。"}, "Q": "查询2025年第三季度出口业务占比超过10%的中药公司，用表格列出其出口占比、营业总收入增长率，并用折线图展示它们的营收增长趋势"}]</t>
+          <t>[{"A": {"content": "抱歉，当前数据库没有出口业务相关字段，无法直接计算出口业务占比。"}, "Q": "查询2025年第三季度出口业务占比超过10%的中药公司，用表格列出其出口占比、营业总收入增长率，并用折线图展示它们的营收增长趋势"}]</t>
         </is>
       </c>
     </row>
@@ -3233,13 +3259,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SELECT AVG(bs.asset_liability_ratio) AS avg_asset_liability_ratio
-FROM balance_sheet bs
-JOIN company_basic_info cbi 
-    ON bs.stock_code = cbi.stock_code
-WHERE bs.report_year = 2025
-    AND bs.report_period = 'Q3'
-    AND cbi.csrc_industry = '中药'</t>
+          <t>SELECT COUNT(*) AS company_record_count, COUNT(asset_liability_ratio) AS valid_sample_count, ROUND(AVG(asset_liability_ratio), 2) AS avg_asset_liability_ratio, ROUND(MIN(asset_liability_ratio), 2) AS min_asset_liability_ratio, ROUND(MAX(asset_liability_ratio), 2) AS max_asset_liability_ratio FROM balance_sheet WHERE report_year = 2025 AND report_period = 'Q3'</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3249,7 +3269,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>[{"A": {"content": "的资产负债率(%)，请问您想查询哪个报告期的数据？（如：2025年第三季度、2024年度）"}, "Q": "中药公司的资产负债率情况如何"}, {"A": {"content": "## 分析结果\n\n**当前无法提供该数据。**\n\n查询结果显示，系统中暂无2025年第三季度66家中药上市公司的资产负债率均值数据（返回值为null）。\n\n---\n\n**可能原因：**\n- 数据尚未更新至2025年Q3\n- 该数据不在当前数据库覆盖范围内\n\n**建议：**\n- 确认数据库是否已收录2025年第三季度财报数据\n- 可尝试查询最近可用季度的数据作为参考"}, "Q": "2025年第三季度，66家中药上市公司的资产负债率均值是多少"}]</t>
+          <t>[{"A": {"content": "## 分析结果\n\n按当前数据库中 2025 年第三季度资产负债表记录统计，可查询到 67 条公司记录，其中 44 条资产负债率为非空值。按非空样本计算，中药公司资产负债率均值为 31.60%。\n\n从分布看，资产负债率最高的公司为太极集团 73.07%，其次为新里程 69.13%、太龙药业 55.88%；资产负债率最低的公司为康弘药业 7.30%、新光药业 7.33%、嘉应制药 8.49%。整体来看，样本公司资产负债率差异较大，平均水平约为三成。"}, "Q": "中药公司的资产负债率情况如何"}, {"A": {"content": "## 分析结果\n\n2025 年第三季度，当前数据库中可查询到 67 条中药公司资产负债表记录，其中 44 条资产负债率为非空值。按非空样本计算，资产负债率均值为 31.60%。\n\n因此，2025 年第三季度中药上市公司的资产负债率平均水平约为 31.60%。"}, "Q": "2025年第三季度，66家中药上市公司的资产负债率均值是多少"}]</t>
         </is>
       </c>
     </row>
